--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 06,08,26 бррсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 06,08,26 бррсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AEF6E44-4D05-4C6D-A1C9-1B48345AD74F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D965A3C-1F4D-44CB-9EA9-780A6397D158}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="172">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -544,6 +544,9 @@
   </si>
   <si>
     <t>дубль</t>
+  </si>
+  <si>
+    <t>нет заказа</t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1301,9 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="7"/>
-      <c r="AH4" s="9"/>
+      <c r="AH4" s="9" t="s">
+        <v>171</v>
+      </c>
       <c r="AI4" s="1"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="1"/>
@@ -5532,7 +5537,7 @@
         <v>130</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" ref="Q19:Q66" si="20">14*P39-O39-F39</f>
+        <f t="shared" ref="Q39:Q52" si="20">14*P39-O39-F39</f>
         <v>485</v>
       </c>
       <c r="R39" s="5">
